--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,22 +79,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
   </si>
 </sst>
 </file>
@@ -638,16 +647,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -661,16 +673,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,16 +699,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -707,16 +725,19 @@
         <v>23</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>23</v>
       </c>
-      <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +802,7 @@
         <v>71.43000000000001</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -833,7 +854,7 @@
         <v>90.48</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,16 +871,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,22 +922,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920211</v>
+        <v>23330051920320</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -924,24 +945,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920393</v>
+        <v>23330051920278</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920280</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -699,16 +699,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H4">
         <v>7.9</v>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -890,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,22 +931,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920320</v>
+        <v>23330051920211</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -945,39 +954,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920278</v>
+        <v>23330051920320</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920280</v>
+        <v>23330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -986,7 +995,30 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920280</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -91,6 +97,12 @@
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -101,6 +113,12 @@
   </si>
   <si>
     <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
@@ -899,7 +917,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -931,16 +949,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920211</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -949,75 +967,121 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920320</v>
+        <v>23330051920195</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920278</v>
+        <v>23330051920211</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920280</v>
+        <v>23330051920320</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920278</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920280</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -85,15 +85,15 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
@@ -103,15 +103,15 @@
     <t>MIRON</t>
   </si>
   <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -121,13 +121,13 @@
     <t>BRAYAN</t>
   </si>
   <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
@@ -606,10 +606,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -618,7 +618,7 @@
         <v>22</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -749,10 +749,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>23</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -892,10 +892,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>23</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>8.9</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920211</v>
+        <v>23330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1010,15 +1010,15 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920320</v>
+        <v>23330051920211</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1033,15 +1033,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920278</v>
+        <v>23330051920320</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1056,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>1</v>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,58 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>VALERIO</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
+    <t>SERGIO JOSUE</t>
   </si>
   <si>
     <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
   </si>
 </sst>
 </file>
@@ -609,16 +573,16 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -752,16 +716,16 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -820,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -846,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -872,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -895,19 +859,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,16 +913,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920183</v>
+        <v>23330051920332</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -967,122 +931,30 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920195</v>
+        <v>23330051920278</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920278</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920211</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920320</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920280</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20241.xlsx
@@ -79,22 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>VERA</t>
+    <t>VALERIO</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>VALERIO</t>
+    <t>OSCAR ALEXANDER</t>
   </si>
   <si>
     <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920332</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -928,15 +928,15 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920278</v>
+        <v>23330051920332</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -951,10 +951,10 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
